--- a/outputs/398-14.xlsx
+++ b/outputs/398-14.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="24">
   <si>
     <t xml:space="preserve">ITEM</t>
   </si>
@@ -214,45 +214,49 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -447,147 +451,147 @@
   <dimension ref="A1:F1000"/>
   <sheetFormatPr defaultColWidth="14.4296875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="1" style="0" width="20.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="7" style="0" width="8.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="1" style="1" width="20.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="7" style="1" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="3" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="3" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="3" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1603,146 +1607,146 @@
   <dimension ref="A1:F1000"/>
   <sheetFormatPr defaultColWidth="14.4296875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="1" style="0" width="8.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="1" style="1" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="3" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="3" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="3" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="F7" s="2"/>
+      <c r="F7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2756,125 +2760,125 @@
   <dimension ref="A1:E1000"/>
   <sheetFormatPr defaultColWidth="14.4296875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="1" style="0" width="8.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="1" style="1" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="3" t="n">
         <v>120</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="3" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="3" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="3" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="3" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="3" t="n">
         <v>6</v>
       </c>
     </row>
@@ -3890,142 +3894,142 @@
   <dimension ref="A1:E1000"/>
   <sheetFormatPr defaultColWidth="14.4296875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="1" style="0" width="8.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="1" style="1" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="3" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="3" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="3" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="3" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5040,215 +5044,215 @@
   <dimension ref="A1:G1000"/>
   <sheetFormatPr defaultColWidth="14.4296875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="1" style="0" width="8.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="8" style="0" width="8.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="1" style="1" width="8.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="8" style="1" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5" t="n">
+      <c r="E2" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="F2" s="6" t="n">
+      <c r="F2" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="G2" s="6" t="n">
+      <c r="G2" s="7" t="n">
         <v>280</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="E3" s="6" t="n">
         <v>270</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="F3" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="G3" s="7" t="n">
         <v>243</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="E4" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F4" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="G4" s="7" t="n">
         <v>57</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="6" t="n">
         <v>70</v>
       </c>
-      <c r="F5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="6" t="n">
+      <c r="F5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="7" t="n">
         <v>70</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="6" t="n">
         <v>72</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="G6" s="7" t="n">
         <v>62</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F7" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="G7" s="7" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="F8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="6" t="n">
+      <c r="F8" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="7" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="n">
+      <c r="A9" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="7" t="n">
+      <c r="F9" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="G9" s="9" t="n">
+      <c r="G9" s="10" t="n">
         <v>-5</v>
       </c>
     </row>
